--- a/media/exports/reports/2026-10/cash-payroll.xlsx
+++ b/media/exports/reports/2026-10/cash-payroll.xlsx
@@ -12,7 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="Cash_at_bank_6_Oct">'Report'!$B$8</definedName>
+    <definedName name="Wages_to_pay_in_November">'Report'!$B$9</definedName>
+    <definedName name="After_the_tightest_pay_run_26_Nov">'Report'!$B$10</definedName>
+    <definedName name="Lowest_point_next_13_weeks">'Report'!$B$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$I$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$84</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -71,12 +78,12 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="002F7A5D"/>
+      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="0025342A"/>
+      <color rgb="002F7A5D"/>
     </font>
   </fonts>
   <fills count="3">
@@ -123,16 +130,18 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -216,6 +225,326 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>November: where the cash comes from and goes (forecast)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>November: where the cash comes from and goes (forecast)</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="#,##0;(#,##0)"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$15:$A$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$15:$B$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Cash at bank by date</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Cash at bank</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$6:$A$96</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$E$6:$E$96</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="7"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2070000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="cash_payroll_Data" displayName="cash_payroll_Data" ref="A5:E96" headerRowCount="1">
+  <autoFilter ref="A5:E96"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Actual or forecast"/>
+    <tableColumn id="3" name="Money in"/>
+    <tableColumn id="4" name="Money out"/>
+    <tableColumn id="5" name="Cash at bank"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -507,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -531,14 +860,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -636,114 +965,90 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Cash at bank was $47,244 at 2pm on 6 October. November has 2 pay runs ($76,500). The tightest is 26 November: $43,014 left after paying wages, $4,764 more than a pay run in reserve. The lowest point in the 13 weeks is $1,159 on 30 November.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>19 invoices ($70,404) are already past the customer's usual payment date; the forecast assumes they arrive within a week. Without them, 26 November would be ($27,390).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Cash at bank, every day: actual to 6 Oct, then forecast to 5 Jan: every month is on the Data sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
           <t>November: where the cash comes from and goes (forecast)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>November: where the cash comes from and goes (forecast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Unpaid invoices collected</t>
         </is>
       </c>
-      <c r="B23" s="6">
+      <c r="B15" s="6">
         <f>Workings!B53</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>New work collected</t>
         </is>
       </c>
-      <c r="B24" s="6">
+      <c r="B16" s="6">
         <f>Workings!B60</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Wages (2 pay runs)</t>
         </is>
       </c>
-      <c r="B25" s="6">
+      <c r="B17" s="6">
         <f>Workings!B69</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Suppliers and overheads</t>
         </is>
       </c>
-      <c r="B26" s="6">
+      <c r="B18" s="6">
         <f>Workings!B78</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Tax, interest and equipment finance</t>
         </is>
       </c>
-      <c r="B27" s="6">
+      <c r="B19" s="6">
         <f>Workings!B84</f>
         <v/>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Cash at bank, every day: actual to 6 Oct, then forecast to 5 Jan: every month is on the Data sheet.</t>
+        </is>
+      </c>
+    </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>13 weeks, week by week</t>
         </is>
@@ -797,611 +1102,611 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>13 Oct</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>$47,244</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>$90,790</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>$138,034</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>$47,244</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>20 Oct</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>$138,034</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>$12,900</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>$6,454</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>($38,250)</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>($55,080)</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>$64,058</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="I32" s="11" t="inlineStr">
         <is>
           <t>$47,285</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>$64,058</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>$9,800</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>$6,454</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>$80,311</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
         <is>
           <t>$65,348</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>3 Nov</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>$80,311</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>$88,700</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>$6,454</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>($38,250)</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>($55,080)</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>($13,097)</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>$69,038</t>
         </is>
       </c>
-      <c r="I34" s="12" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
         <is>
           <t>$47,826</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>10 Nov</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>$69,038</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>$23,176</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>$92,215</t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>$70,329</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>17 Nov</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>$92,215</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>$34,325</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>($38,250)</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>($55,080)</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>$33,210</t>
         </is>
       </c>
-      <c r="I36" s="12" t="inlineStr">
+      <c r="I36" s="11" t="inlineStr">
         <is>
           <t>$31,919</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>24 Nov</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>$33,210</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>$34,325</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>$67,534</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>$40,074</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>1 Dec</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>$67,534</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>$74,825</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>($38,250)</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>($55,080)</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>($6,080)</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>$42,949</t>
         </is>
       </c>
-      <c r="I38" s="12" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>$1,159</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>8 Dec</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>$42,949</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>$34,325</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>$77,274</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>$49,814</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>15 Dec</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>$77,274</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>$34,325</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>($38,250)</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>($55,080)</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>$18,269</t>
         </is>
       </c>
-      <c r="I40" s="12" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>$18,269</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>22 Dec</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>$18,269</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>$34,325</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>$52,594</t>
         </is>
       </c>
-      <c r="I41" s="12" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>$25,134</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>29 Dec</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>$52,594</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>$34,325</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>($38,250)</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>($5,000)</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>$43,669</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>$28,074</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>5 Jan</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>$43,669</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>$74,825</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>($55,080)</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>($1,080)</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>$62,334</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
+      <c r="I43" s="11" t="inlineStr">
         <is>
           <t>$41,739</t>
         </is>
@@ -1409,7 +1714,7 @@
     </row>
     <row r="44"/>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Invoices past the customer's usual payment date ($70,404)</t>
         </is>
@@ -1443,289 +1748,319 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Wacol warehouse switchboard</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>4 Sep</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>$46,800</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Milton office tower</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>$4,200</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>Rocklea factory</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>$3,900</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Bulimba school</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>$2,800</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>West End brewery</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>$2,600</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>$2,400</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Newstead gym</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>$1,600</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Call-out 15, September</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>15 Sep</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>$775</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Call-out 9, September</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>22 Sep</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>$762</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Call-out 32, September</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>21 Sep</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>$597</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
     <row r="57"/>
-    <row r="58"/>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Cash at bank was $47,244 at 2pm on 6 October. November has 2 pay runs ($76,500). The tightest is 26 November: $43,014 left after paying wages, $4,764 more than a pay run in reserve. The lowest point in the 13 weeks is $1,159 on 30 November.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>19 invoices ($70,404) are already past the customer's usual payment date; the forecast assumes they arrive within a week. Without them, 26 November would be ($27,390).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A62:D62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1734,6 +2069,7 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="28" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1762,14 +2098,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2688,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2392,14 +2728,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4684,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4359,5 +4695,9 @@
     <brk id="61" min="0" max="16383" man="1"/>
     <brk id="91" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-10/cash-payroll.xlsx
+++ b/media/exports/reports/2026-10/cash-payroll.xlsx
@@ -13,11 +13,11 @@
   </sheets>
   <definedNames>
     <definedName name="Cash_at_bank_6_Oct">'Report'!$B$8</definedName>
-    <definedName name="Wages_to_pay_in_November">'Report'!$B$9</definedName>
+    <definedName name="Paid_to_employees_in_November">'Report'!$B$9</definedName>
     <definedName name="After_the_tightest_pay_run_26_Nov">'Report'!$B$10</definedName>
     <definedName name="Lowest_point_next_13_weeks">'Report'!$B$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$I$62</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$84</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$J$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$108</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$96</definedName>
   </definedNames>
@@ -310,7 +310,7 @@
             </spPr>
           </dPt>
           <dPt>
-            <idx val="4"/>
+            <idx val="5"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="B42318"/>
@@ -333,12 +333,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$15:$A$19</f>
+              <f>'Report'!$A$15:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$15:$B$19</f>
+              <f>'Report'!$B$15:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -488,7 +488,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2070000"/>
+    <ext cx="5400000" cy="2340000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -848,6 +848,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -867,7 +868,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -875,7 +876,7 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>A 13-week cash forecast from 2pm on 6 October: cash at bank, plus what customers owe on their usual payment dates and new work at its recent rate, less pay runs, supplier bills, tax and finance on their due dates. Every day opens its workings.</t>
+          <t>A 13-week cash forecast from 2pm on 6 October: cash at bank, plus what customers owe on their usual payment dates and new work at its recent rate, less pay runs, supplier bills, the BAS and finance on their due dates. Every day opens its workings.</t>
         </is>
       </c>
     </row>
@@ -916,7 +917,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wages to pay in November</t>
+          <t>Paid to employees in November</t>
         </is>
       </c>
       <c r="B9" s="6">
@@ -925,7 +926,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>2 fortnightly pay runs</t>
+          <t>2 fortnightly pay runs, net pay + super</t>
         </is>
       </c>
     </row>
@@ -936,12 +937,12 @@
         </is>
       </c>
       <c r="B10" s="6">
-        <f>Workings!B33</f>
+        <f>Workings!B34</f>
         <v/>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>buffer: one pay run, $38,250</t>
+          <t>buffer: one pay run, $36,611</t>
         </is>
       </c>
     </row>
@@ -952,7 +953,7 @@
         </is>
       </c>
       <c r="B11" s="6">
-        <f>Workings!B46</f>
+        <f>Workings!B48</f>
         <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -984,7 +985,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>Workings!B53</f>
+        <f>Workings!B55</f>
         <v/>
       </c>
     </row>
@@ -995,18 +996,18 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>Workings!B60</f>
+        <f>Workings!B62</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Wages (2 pay runs)</t>
+          <t>Pay runs (2)</t>
         </is>
       </c>
       <c r="B17" s="6">
-        <f>Workings!B69</f>
+        <f>Workings!B71</f>
         <v/>
       </c>
     </row>
@@ -1017,203 +1018,126 @@
         </is>
       </c>
       <c r="B18" s="6">
-        <f>Workings!B78</f>
+        <f>Workings!B84</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tax, interest and equipment finance</t>
+          <t>BAS (GST and PAYG)</t>
         </is>
       </c>
       <c r="B19" s="6">
-        <f>Workings!B84</f>
+        <f>Workings!B90</f>
         <v/>
       </c>
     </row>
-    <row r="20"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Interest and equipment finance</t>
+        </is>
+      </c>
+      <c r="B20" s="6">
+        <f>Workings!B97</f>
+        <v/>
+      </c>
+    </row>
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Cash at bank, every day: actual to 6 Oct, then forecast to 5 Jan: every month is on the Data sheet.</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Cash at bank, every day: actual to 6 Oct, then forecast to 5 Jan: every month is on the Data sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>13 weeks, week by week</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Week ending</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Cash at start</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Unpaid invoices collected</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>New work collected</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Wages</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Pay runs</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Suppliers and overheads</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Tax, interest and finance</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>BAS (GST and PAYG)</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Interest and finance</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Cash at end</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Lowest in the week</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>13 Oct</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>$47,244</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>$90,790</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>$138,034</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>$47,244</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>20 Oct</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>$138,034</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>$12,900</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>$6,454</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>($38,250)</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>($55,080)</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>$64,058</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>$47,285</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>27 Oct</t>
+          <t>13 Oct</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>$64,058</t>
+          <t>$115,211</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$111,493</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>$6,454</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
@@ -1233,165 +1157,185 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>$80,311</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>$65,348</t>
+          <t>$226,704</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>$115,211</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>3 Nov</t>
+          <t>20 Oct</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>$80,311</t>
+          <t>$226,704</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>$88,700</t>
+          <t>$15,840</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>$6,454</t>
+          <t>$7,823</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>($38,250)</t>
+          <t>($36,611)</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>($55,080)</t>
+          <t>($60,588)</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>($13,097)</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>$69,038</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>$47,826</t>
+          <t>$153,168</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>$132,634</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>10 Nov</t>
+          <t>27 Oct</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>$69,038</t>
+          <t>$153,168</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
+          <t>$12,100</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>$7,824</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>$23,176</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>$92,215</t>
-        </is>
-      </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>$70,329</t>
+          <t>$173,092</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>$154,733</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>17 Nov</t>
+          <t>3 Nov</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>$92,215</t>
+          <t>$173,092</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$109,285</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>$34,325</t>
+          <t>$7,823</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>($38,250)</t>
+          <t>($36,611)</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>($55,080)</t>
+          <t>($60,588)</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>($86,253)</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>$33,210</t>
+          <t>($6,080)</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>$31,919</t>
+          <t>$100,668</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>$67,057</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>24 Nov</t>
+          <t>10 Nov</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>$33,210</t>
+          <t>$100,668</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -1401,7 +1345,7 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>$34,325</t>
+          <t>$28,746</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -1421,24 +1365,29 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>$67,534</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>$40,074</t>
+          <t>$129,414</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>$102,233</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>1 Dec</t>
+          <t>17 Nov</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>$67,534</t>
+          <t>$129,414</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -1448,44 +1397,49 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>$74,825</t>
+          <t>$42,693</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>($38,250)</t>
+          <t>($36,611)</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>($55,080)</t>
+          <t>($60,588)</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>($6,080)</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>$42,949</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>$1,159</t>
+          <t>$74,908</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>$73,344</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>8 Dec</t>
+          <t>24 Nov</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>$42,949</t>
+          <t>$74,908</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -1495,7 +1449,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>$34,325</t>
+          <t>$42,694</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -1515,24 +1469,29 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>$77,274</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>$49,814</t>
+          <t>$117,602</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>$83,447</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>15 Dec</t>
+          <t>1 Dec</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>$77,274</t>
+          <t>$117,602</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -1542,17 +1501,17 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>$34,325</t>
+          <t>$92,578</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>($38,250)</t>
+          <t>($36,611)</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>($55,080)</t>
+          <t>($60,588)</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -1562,24 +1521,29 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>$18,269</t>
+          <t>($6,080)</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>$18,269</t>
+          <t>$106,901</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>$55,452</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>22 Dec</t>
+          <t>8 Dec</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>$18,269</t>
+          <t>$106,901</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -1589,7 +1553,7 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>$34,325</t>
+          <t>$42,694</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
@@ -1609,24 +1573,29 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>$52,594</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>$25,134</t>
+          <t>$149,595</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>$115,440</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>29 Dec</t>
+          <t>15 Dec</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>$52,594</t>
+          <t>$149,595</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -1636,185 +1605,245 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>$34,325</t>
+          <t>$42,693</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>($38,250)</t>
+          <t>($36,611)</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
+          <t>($60,588)</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>($5,000)</t>
-        </is>
-      </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>$43,669</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>$28,074</t>
+          <t>$95,089</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>$95,089</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
+          <t>22 Dec</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>$95,089</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>$42,694</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>$137,783</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>$103,628</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>29 Dec</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>$137,783</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>$42,693</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>($36,611)</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>($5,000)</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>$138,865</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>$118,249</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
           <t>5 Jan</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>$43,669</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>$138,865</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>$74,825</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>$89,449</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>($55,080)</t>
-        </is>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>($60,588)</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>($1,080)</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>$62,334</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>$41,739</t>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Invoices past the customer's usual payment date ($70,404)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>$166,646</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>$144,159</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Invoices past the customer's usual payment date ($86,470): the forecast assumes these arrive within a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Customer or job</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Invoiced</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Amount (incl. GST)</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Usually pays in (days)</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Days since invoiced</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>Wacol warehouse switchboard</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>4 Sep</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>$46,800</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Milton office tower</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>1 Sep</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>$4,200</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Wacol warehouse switchboard</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>1 Sep</t>
+          <t>4 Sep</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>$3,900</t>
+          <t>$57,640</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -1824,14 +1853,14 @@
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -1841,7 +1870,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>$2,800</t>
+          <t>$5,170</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -1858,7 +1887,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Rocklea factory</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -1868,7 +1897,7 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>$2,600</t>
+          <t>$4,785</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -1885,7 +1914,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Bulimba school</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -1895,7 +1924,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>$2,400</t>
+          <t>$3,465</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -1912,7 +1941,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>West End brewery</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -1922,7 +1951,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>$1,600</t>
+          <t>$3,190</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
@@ -1939,135 +1968,449 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Call-out 15, September</t>
+          <t>Kangaroo Point townhouses</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>15 Sep</t>
+          <t>1 Sep</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>$775</t>
+          <t>$2,970</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Call-out 9, September</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>22 Sep</t>
+          <t>1 Sep</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>$762</t>
+          <t>$1,980</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
+          <t>Call-out 15, September</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>$932</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 9, September</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>22 Sep</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>$917</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
           <t>Call-out 32, September</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>21 Sep</t>
         </is>
       </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>$597</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>$706</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 28, September</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>25 Sep</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>$659</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 49, September</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>27 Sep</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>$645</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 63, September</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>$635</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 50, September</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>28 Sep</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>$598</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 22, September</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>17 Sep</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>$535</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 38, September</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>23 Sep</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>$459</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 26, September</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>26 Sep</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>$441</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 31, September</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>13 Sep</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>$416</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>Call-out 43, September</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>16 Sep</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>$327</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>How the 30 September forecast has done so far</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="45" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>For 5 October it said $133,401; the bank says $104,453, $28,948 less. $31,304 of it is 11 invoices expected by then and not yet paid, the largest Milton office tower ($5,170). (Workings sheet: "From gross margin to profit".)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Cash at bank was $47,244 at 2pm on 6 October. November has 2 pay runs ($76,500). The tightest is 26 November: $43,014 left after paying wages, $4,764 more than a pay run in reserve. The lowest point in the 13 weeks is $1,159 on 30 November.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Cash at bank was $115,211 at 2pm on 6 October. November has 2 pay runs ($73,222). The tightest is 26 November: $98,068 left after paying wages, $61,457 more than a pay run in reserve. The lowest point in the 13 weeks is $55,452 on 30 November.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>19 invoices ($70,404) are already past the customer's usual payment date; the forecast assumes they arrive within a week. Without them, 26 November would be ($27,390).</t>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64"/>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>19 invoices ($86,470) are already past the customer's usual payment date; the forecast assumes they arrive within a week. Without them, the lowest point would be ($31,018). The July to September BAS ($86,253) is due 28 October: GST $32,817, PAYG withheld $47,754 and the PAYG instalment $5,682.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A73:D73"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="28" min="0" max="16383" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="30" min="0" max="16383" man="1"/>
+    <brk id="71" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2079,7 +2422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -2105,7 +2448,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2492,7 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>363114</v>
+        <v>445130</v>
       </c>
     </row>
     <row r="10">
@@ -2159,7 +2502,7 @@
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>-403870</v>
+        <v>-417919</v>
       </c>
     </row>
     <row r="11">
@@ -2192,7 +2535,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Number of fortnightly pay runs × the last pay run</t>
+          <t>Number of fortnightly pay runs × the cash each one takes</t>
         </is>
       </c>
     </row>
@@ -2207,11 +2550,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Last pay run (1 October)</t>
+          <t>Last pay run, net pay + super (1 October)</t>
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>38250</v>
+        <v>36611</v>
       </c>
     </row>
     <row r="19">
@@ -2227,7 +2570,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Wages paid in November</t>
+          <t>Paid to employees and their super funds in November</t>
         </is>
       </c>
       <c r="B20" s="16">
@@ -2238,7 +2581,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Wages include all on-costs. Fortnightly pay means two months a year have three pay runs.</t>
+          <t>Each pay run is a 26th of the year's gross wages: net pay and super leave the bank on pay day, and the PAYG withheld goes to the ATO with the BAS. Fortnightly pay means two months a year have three pay runs.</t>
         </is>
       </c>
     </row>
@@ -2273,13 +2616,13 @@
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>74399.4090909092</v>
+        <v>126140</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unpaid invoices expected</t>
+          <t>Unpaid invoices expected (incl. GST)</t>
         </is>
       </c>
       <c r="B28" s="14" t="n">
@@ -2289,27 +2632,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>New work expected to be paid</t>
+          <t>New work expected to be paid (incl. GST)</t>
         </is>
       </c>
       <c r="B29" s="14" t="n">
-        <v>6864.984848484848</v>
+        <v>8539</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pay run</t>
+          <t>Pay run (net pay + super)</t>
         </is>
       </c>
       <c r="B30" s="14" t="n">
-        <v>-38250</v>
+        <v>-36611</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Suppliers and overheads</t>
+          <t>Suppliers and overheads (incl. GST)</t>
         </is>
       </c>
       <c r="B31" s="14" t="n">
@@ -2319,7 +2662,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tax, interest and equipment finance</t>
+          <t>BAS: GST, PAYG withheld and PAYG instalment</t>
         </is>
       </c>
       <c r="B32" s="14" t="n">
@@ -2327,377 +2670,563 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Interest and equipment finance</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Cash at bank, end of the day</t>
         </is>
       </c>
-      <c r="B33" s="16">
-        <f>B27+B28+B29+B30+B31+B32</f>
+      <c r="B34" s="16">
+        <f>B27+B28+B29+B30+B31+B32+B33</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Forecast.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36"/>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Forecast cash at bank, 30 Nov 2026</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Yesterday's cash + money in − money out</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>30 Nov</t>
         </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Cash at bank, end of the day before</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="n">
-        <v>61027.86363636375</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Unpaid invoices expected</t>
+          <t>Cash at bank, end of the day before</t>
         </is>
       </c>
       <c r="B41" s="14" t="n">
-        <v>0</v>
+        <v>106607</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>New work expected to be paid</t>
+          <t>Unpaid invoices expected (incl. GST)</t>
         </is>
       </c>
       <c r="B42" s="14" t="n">
-        <v>1290.742424242424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pay run</t>
+          <t>New work expected to be paid (incl. GST)</t>
         </is>
       </c>
       <c r="B43" s="14" t="n">
-        <v>0</v>
+        <v>15513</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Suppliers and overheads</t>
+          <t>Pay run (net pay + super)</t>
         </is>
       </c>
       <c r="B44" s="14" t="n">
-        <v>-55080</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tax, interest and equipment finance</t>
+          <t>Suppliers and overheads (incl. GST)</t>
         </is>
       </c>
       <c r="B45" s="14" t="n">
+        <v>-60588</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BAS: GST, PAYG withheld and PAYG instalment</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Interest and equipment finance</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="n">
         <v>-6080</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>Cash at bank, end of the day</t>
         </is>
       </c>
-      <c r="B46" s="16">
-        <f>B40+B41+B42+B43+B44+B45</f>
+      <c r="B48" s="16">
+        <f>B41+B42+B43+B44+B45+B46+B47</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Forecast.</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>Unpaid invoices collected in November</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Each invoice unpaid at the start, on its customer's usual payment date</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr"/>
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>Each invoice unpaid at the start, on its customer's usual payment date (next banking day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Expected in the month</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n">
-        <v>33000</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>Expected in the month (incl. GST)</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="n">
+        <v>90585</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>42 invoices unpaid at 2pm on 6 October; overdue ones assumed a week from then.</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="13" t="inlineStr">
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>New work collected in November</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Contract fees (1st of the month, on each contract's terms) + installations and call-outs at the last three months' run rate</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr"/>
-      <c r="B59" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>Expected in the month</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="n">
-        <v>127442</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Run rate from July, August, September.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>Expected in the month (incl. GST)</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="n">
+        <v>158391</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Run rate from July, August, September. Every day's amount is in whole dollars, so the days add up to this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Pay runs in November</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>Number of fortnightly pay runs × the last pay run</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr"/>
-      <c r="B66" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>Number of fortnightly pay runs × the cash each one takes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr"/>
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Last pay run (1 October)</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="n">
-        <v>38250</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Last pay run, net pay + super (1 October)</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="n">
+        <v>36611</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Pay runs in November (12 Nov, 26 Nov)</t>
         </is>
       </c>
-      <c r="B68" s="14" t="n">
+      <c r="B70" s="14" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="15" t="inlineStr">
-        <is>
-          <t>Wages paid in November</t>
-        </is>
-      </c>
-      <c r="B69" s="16">
-        <f>B67*B68</f>
+    <row r="71">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>Paid to employees and their super funds in November</t>
+        </is>
+      </c>
+      <c r="B71" s="16">
+        <f>B69*B70</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Wages include all on-costs. Fortnightly pay means two months a year have three pay runs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" s="13" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Each pay run is a 26th of the year's gross wages: net pay and super leave the bank on pay day, and the PAYG withheld goes to the ATO with the BAS. Fortnightly pay means two months a year have three pay runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>Suppliers and overheads in November</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>Last month's bills (trade creditors) + the month's overheads, paid on the 15th and at month end</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr"/>
-      <c r="B75" s="5" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Last month's bills (trade creditors) + the month's overheads, half on the 15th and half at month end, on banking days</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr"/>
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Bills owed for October's materials and subcontractors (estimate: the latest month's)</t>
-        </is>
-      </c>
-      <c r="B76" s="14" t="n">
-        <v>78060</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Overheads (at September's level)</t>
-        </is>
-      </c>
-      <c r="B77" s="14" t="n">
-        <v>32100</v>
-      </c>
-    </row>
     <row r="78">
-      <c r="A78" s="15" t="inlineStr">
-        <is>
-          <t>Paid in the month</t>
-        </is>
-      </c>
-      <c r="B78" s="16">
-        <f>B76+B77</f>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>October's bills for materials and subcontractors, incl. GST (estimate: the latest month's)</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="n">
+        <v>85866</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Overheads, incl. GST (at September's level)</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="n">
+        <v>35310</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>November's supplier bills</t>
+        </is>
+      </c>
+      <c r="B80" s="14">
+        <f>B78+B79</f>
         <v/>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80"/>
     <row r="81">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>Tax, interest and equipment finance in November</t>
-        </is>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>October run due 31 October, lands Mon 2 Nov (31 Oct isn't a banking day): paid in November</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="n">
+        <v>-60588</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>Interest + equipment finance repayment (+ the PAYG instalment in Jan, Apr, Jul, Oct)</t>
-        </is>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>November run due 15 November, lands Mon 16 Nov (15 Nov isn't a banking day): paid in November</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="n">
+        <v>-60588</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr"/>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>November run due 30 November: paid in November</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="n">
+        <v>-60588</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t>Paid in the month</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="n">
-        <v>7160</v>
+          <t>Paid in November</t>
+        </is>
+      </c>
+      <c r="B84" s="16">
+        <f>B81+B82+B83</f>
+        <v/>
       </c>
     </row>
     <row r="85"/>
     <row r="86"/>
-    <row r="87"/>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>BAS in November</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>GST on sales − GST credits + PAYG withheld + PAYG instalment, for the quarter, due on the 28th (quarterly, self-lodged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr"/>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>BAS paid in November</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>No BAS falls due in November. The October to December BAS is due 28 February.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>Interest and equipment finance in November</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>Interest at month end + the equipment finance repayment on the 28th (no GST on either)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr"/>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>Paid in the month</t>
+        </is>
+      </c>
+      <c r="B97" s="16" t="n">
+        <v>7160</v>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>Forecast made 30 September against the bank, 5 October</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>Actual cash − forecast cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr"/>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>5 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Forecast for 5 October</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="n">
+        <v>133401</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Actual, 5 October</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>104453</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Actual − forecast</t>
+        </is>
+      </c>
+      <c r="B105" s="14">
+        <f>B104-B103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Of which: invoices expected by then, not yet paid</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="n">
+        <v>-31304</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>Everything else (timing of other money in and out)</t>
+        </is>
+      </c>
+      <c r="B107" s="16">
+        <f>B105-B106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Not yet paid: Milton office tower $5,170; Chermside retail centre $5,060; Rocklea factory $4,785; Bulimba school $3,465; West End brewery $3,190….</t>
+        </is>
+      </c>
+    </row>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="3" manualBreakCount="3">
+  <rowBreaks count="4" manualBreakCount="4">
     <brk id="23" min="0" max="16383" man="1"/>
-    <brk id="49" min="0" max="16383" man="1"/>
-    <brk id="80" min="0" max="16383" man="1"/>
+    <brk id="51" min="0" max="16383" man="1"/>
+    <brk id="74" min="0" max="16383" man="1"/>
+    <brk id="99" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2735,7 +3264,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2785,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>47244</v>
+        <v>115211</v>
       </c>
     </row>
     <row r="7">
@@ -2800,13 +3329,13 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>684</v>
+        <v>832</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>47928</v>
+        <v>116043</v>
       </c>
     </row>
     <row r="8">
@@ -2821,13 +3350,13 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>19210</v>
+        <v>23599</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>67138</v>
+        <v>139642</v>
       </c>
     </row>
     <row r="9">
@@ -2842,13 +3371,13 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>67630</v>
+        <v>139642</v>
       </c>
     </row>
     <row r="10">
@@ -2869,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>67630</v>
+        <v>139642</v>
       </c>
     </row>
     <row r="11">
@@ -2884,13 +3413,13 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>67630</v>
+        <v>140234</v>
       </c>
     </row>
     <row r="12">
@@ -2905,13 +3434,13 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>70404</v>
+        <v>86470</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>138034</v>
+        <v>226704</v>
       </c>
     </row>
     <row r="13">
@@ -2926,13 +3455,13 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>139325</v>
+        <v>228269</v>
       </c>
     </row>
     <row r="14">
@@ -2947,13 +3476,13 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1291</v>
+        <v>1564</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>-93330</v>
+        <v>-97199</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>47285</v>
+        <v>132634</v>
       </c>
     </row>
     <row r="15">
@@ -2968,13 +3497,13 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>48576</v>
+        <v>134199</v>
       </c>
     </row>
     <row r="16">
@@ -2995,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>48576</v>
+        <v>134199</v>
       </c>
     </row>
     <row r="17">
@@ -3010,13 +3539,13 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>12900</v>
+        <v>0</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>61476</v>
+        <v>134199</v>
       </c>
     </row>
     <row r="18">
@@ -3031,13 +3560,13 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>1291</v>
+        <v>17405</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>62767</v>
+        <v>151604</v>
       </c>
     </row>
     <row r="19">
@@ -3052,13 +3581,13 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>1291</v>
+        <v>1564</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>64058</v>
+        <v>153168</v>
       </c>
     </row>
     <row r="20">
@@ -3073,13 +3602,13 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>65348</v>
+        <v>154733</v>
       </c>
     </row>
     <row r="21">
@@ -3094,13 +3623,13 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>66639</v>
+        <v>156298</v>
       </c>
     </row>
     <row r="22">
@@ -3115,13 +3644,13 @@
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>11091</v>
+        <v>13665</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>77730</v>
+        <v>169963</v>
       </c>
     </row>
     <row r="23">
@@ -3142,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>77730</v>
+        <v>169963</v>
       </c>
     </row>
     <row r="24">
@@ -3163,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>77730</v>
+        <v>169963</v>
       </c>
     </row>
     <row r="25">
@@ -3178,13 +3707,13 @@
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>1291</v>
+        <v>1564</v>
       </c>
       <c r="D25" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>79021</v>
+        <v>171527</v>
       </c>
     </row>
     <row r="26">
@@ -3199,13 +3728,13 @@
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>80311</v>
+        <v>173092</v>
       </c>
     </row>
     <row r="27">
@@ -3220,13 +3749,13 @@
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>-12017</v>
+        <v>-91253</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>69585</v>
+        <v>83404</v>
       </c>
     </row>
     <row r="28">
@@ -3241,13 +3770,13 @@
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>16491</v>
+        <v>20264</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>-38250</v>
+        <v>-36611</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>47826</v>
+        <v>67057</v>
       </c>
     </row>
     <row r="29">
@@ -3262,13 +3791,13 @@
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D29" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>49117</v>
+        <v>68622</v>
       </c>
     </row>
     <row r="30">
@@ -3283,13 +3812,13 @@
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>40500</v>
+        <v>0</v>
       </c>
       <c r="D30" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>89617</v>
+        <v>68622</v>
       </c>
     </row>
     <row r="31">
@@ -3304,13 +3833,13 @@
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="D31" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>122617</v>
+        <v>68622</v>
       </c>
     </row>
     <row r="32">
@@ -3325,13 +3854,13 @@
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>1291</v>
+        <v>92150</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>-56160</v>
+        <v>-61668</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>67747</v>
+        <v>99104</v>
       </c>
     </row>
     <row r="33">
@@ -3346,13 +3875,13 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1291</v>
+        <v>1564</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>69038</v>
+        <v>100668</v>
       </c>
     </row>
     <row r="34">
@@ -3367,13 +3896,13 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>70329</v>
+        <v>102233</v>
       </c>
     </row>
     <row r="35">
@@ -3388,13 +3917,13 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>71620</v>
+        <v>103798</v>
       </c>
     </row>
     <row r="36">
@@ -3409,13 +3938,13 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>6865</v>
+        <v>8538</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>78485</v>
+        <v>112336</v>
       </c>
     </row>
     <row r="37">
@@ -3430,13 +3959,13 @@
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>84059</v>
+        <v>112336</v>
       </c>
     </row>
     <row r="38">
@@ -3451,13 +3980,13 @@
         </is>
       </c>
       <c r="C38" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D38" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>89633</v>
+        <v>112336</v>
       </c>
     </row>
     <row r="39">
@@ -3472,13 +4001,13 @@
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>1291</v>
+        <v>15513</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>90924</v>
+        <v>127849</v>
       </c>
     </row>
     <row r="40">
@@ -3493,13 +4022,13 @@
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>92215</v>
+        <v>129414</v>
       </c>
     </row>
     <row r="41">
@@ -3514,13 +4043,13 @@
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>99080</v>
+        <v>137953</v>
       </c>
     </row>
     <row r="42">
@@ -3535,13 +4064,13 @@
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>6865</v>
+        <v>8538</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>-38250</v>
+        <v>-36611</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>67695</v>
+        <v>109880</v>
       </c>
     </row>
     <row r="43">
@@ -3556,13 +4085,13 @@
         </is>
       </c>
       <c r="C43" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>74560</v>
+        <v>118419</v>
       </c>
     </row>
     <row r="44">
@@ -3577,13 +4106,13 @@
         </is>
       </c>
       <c r="C44" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D44" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>80134</v>
+        <v>118419</v>
       </c>
     </row>
     <row r="45">
@@ -3598,13 +4127,13 @@
         </is>
       </c>
       <c r="C45" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D45" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>85708</v>
+        <v>118419</v>
       </c>
     </row>
     <row r="46">
@@ -3619,13 +4148,13 @@
         </is>
       </c>
       <c r="C46" s="14" t="n">
-        <v>1291</v>
+        <v>15513</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>-55080</v>
+        <v>-60588</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>31919</v>
+        <v>73344</v>
       </c>
     </row>
     <row r="47">
@@ -3640,13 +4169,13 @@
         </is>
       </c>
       <c r="C47" s="14" t="n">
-        <v>1291</v>
+        <v>1564</v>
       </c>
       <c r="D47" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>33210</v>
+        <v>74908</v>
       </c>
     </row>
     <row r="48">
@@ -3661,13 +4190,13 @@
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D48" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>40074</v>
+        <v>83447</v>
       </c>
     </row>
     <row r="49">
@@ -3682,13 +4211,13 @@
         </is>
       </c>
       <c r="C49" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D49" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>46939</v>
+        <v>91986</v>
       </c>
     </row>
     <row r="50">
@@ -3703,13 +4232,13 @@
         </is>
       </c>
       <c r="C50" s="14" t="n">
-        <v>6865</v>
+        <v>8538</v>
       </c>
       <c r="D50" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>53804</v>
+        <v>100524</v>
       </c>
     </row>
     <row r="51">
@@ -3724,13 +4253,13 @@
         </is>
       </c>
       <c r="C51" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D51" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>59379</v>
+        <v>100524</v>
       </c>
     </row>
     <row r="52">
@@ -3745,13 +4274,13 @@
         </is>
       </c>
       <c r="C52" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D52" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>64953</v>
+        <v>100524</v>
       </c>
     </row>
     <row r="53">
@@ -3766,13 +4295,13 @@
         </is>
       </c>
       <c r="C53" s="14" t="n">
-        <v>1291</v>
+        <v>15513</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>66244</v>
+        <v>116037</v>
       </c>
     </row>
     <row r="54">
@@ -3787,13 +4316,13 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>67534</v>
+        <v>117602</v>
       </c>
     </row>
     <row r="55">
@@ -3808,13 +4337,13 @@
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>6865</v>
+        <v>8538</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>74399</v>
+        <v>126140</v>
       </c>
     </row>
     <row r="56">
@@ -3829,13 +4358,13 @@
         </is>
       </c>
       <c r="C56" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>-38250</v>
+        <v>-36611</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>43014</v>
+        <v>98068</v>
       </c>
     </row>
     <row r="57">
@@ -3850,13 +4379,13 @@
         </is>
       </c>
       <c r="C57" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D57" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>49879</v>
+        <v>106607</v>
       </c>
     </row>
     <row r="58">
@@ -3871,13 +4400,13 @@
         </is>
       </c>
       <c r="C58" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D58" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>55454</v>
+        <v>106607</v>
       </c>
     </row>
     <row r="59">
@@ -3892,13 +4421,13 @@
         </is>
       </c>
       <c r="C59" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D59" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>61028</v>
+        <v>106607</v>
       </c>
     </row>
     <row r="60">
@@ -3913,13 +4442,13 @@
         </is>
       </c>
       <c r="C60" s="14" t="n">
-        <v>1291</v>
+        <v>15513</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>-61160</v>
+        <v>-66668</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>1159</v>
+        <v>55452</v>
       </c>
     </row>
     <row r="61">
@@ -3934,13 +4463,13 @@
         </is>
       </c>
       <c r="C61" s="14" t="n">
-        <v>41791</v>
+        <v>51449</v>
       </c>
       <c r="D61" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>42949</v>
+        <v>106901</v>
       </c>
     </row>
     <row r="62">
@@ -3955,13 +4484,13 @@
         </is>
       </c>
       <c r="C62" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D62" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>49814</v>
+        <v>115440</v>
       </c>
     </row>
     <row r="63">
@@ -3976,13 +4505,13 @@
         </is>
       </c>
       <c r="C63" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D63" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>56679</v>
+        <v>123979</v>
       </c>
     </row>
     <row r="64">
@@ -3997,13 +4526,13 @@
         </is>
       </c>
       <c r="C64" s="14" t="n">
-        <v>6865</v>
+        <v>8538</v>
       </c>
       <c r="D64" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>63544</v>
+        <v>132517</v>
       </c>
     </row>
     <row r="65">
@@ -4018,13 +4547,13 @@
         </is>
       </c>
       <c r="C65" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D65" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>69119</v>
+        <v>132517</v>
       </c>
     </row>
     <row r="66">
@@ -4039,13 +4568,13 @@
         </is>
       </c>
       <c r="C66" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D66" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>74693</v>
+        <v>132517</v>
       </c>
     </row>
     <row r="67">
@@ -4060,13 +4589,13 @@
         </is>
       </c>
       <c r="C67" s="14" t="n">
-        <v>1291</v>
+        <v>15513</v>
       </c>
       <c r="D67" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>75984</v>
+        <v>148030</v>
       </c>
     </row>
     <row r="68">
@@ -4081,13 +4610,13 @@
         </is>
       </c>
       <c r="C68" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D68" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>77274</v>
+        <v>149595</v>
       </c>
     </row>
     <row r="69">
@@ -4102,13 +4631,13 @@
         </is>
       </c>
       <c r="C69" s="14" t="n">
-        <v>6865</v>
+        <v>8538</v>
       </c>
       <c r="D69" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>84139</v>
+        <v>158133</v>
       </c>
     </row>
     <row r="70">
@@ -4123,13 +4652,13 @@
         </is>
       </c>
       <c r="C70" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D70" s="14" t="n">
-        <v>-38250</v>
+        <v>-36611</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>52754</v>
+        <v>130061</v>
       </c>
     </row>
     <row r="71">
@@ -4144,13 +4673,13 @@
         </is>
       </c>
       <c r="C71" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D71" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>59619</v>
+        <v>138600</v>
       </c>
     </row>
     <row r="72">
@@ -4165,13 +4694,13 @@
         </is>
       </c>
       <c r="C72" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D72" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>65193</v>
+        <v>138600</v>
       </c>
     </row>
     <row r="73">
@@ -4186,13 +4715,13 @@
         </is>
       </c>
       <c r="C73" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D73" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>70768</v>
+        <v>138600</v>
       </c>
     </row>
     <row r="74">
@@ -4207,13 +4736,13 @@
         </is>
       </c>
       <c r="C74" s="14" t="n">
-        <v>1291</v>
+        <v>15512</v>
       </c>
       <c r="D74" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>72058</v>
+        <v>154112</v>
       </c>
     </row>
     <row r="75">
@@ -4228,13 +4757,13 @@
         </is>
       </c>
       <c r="C75" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>-55080</v>
+        <v>-60588</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>18269</v>
+        <v>95089</v>
       </c>
     </row>
     <row r="76">
@@ -4249,13 +4778,13 @@
         </is>
       </c>
       <c r="C76" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D76" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>25134</v>
+        <v>103628</v>
       </c>
     </row>
     <row r="77">
@@ -4270,13 +4799,13 @@
         </is>
       </c>
       <c r="C77" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D77" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>31999</v>
+        <v>112167</v>
       </c>
     </row>
     <row r="78">
@@ -4291,13 +4820,13 @@
         </is>
       </c>
       <c r="C78" s="14" t="n">
-        <v>6865</v>
+        <v>8538</v>
       </c>
       <c r="D78" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E78" s="14" t="n">
-        <v>38864</v>
+        <v>120705</v>
       </c>
     </row>
     <row r="79">
@@ -4312,13 +4841,13 @@
         </is>
       </c>
       <c r="C79" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D79" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>44438</v>
+        <v>120705</v>
       </c>
     </row>
     <row r="80">
@@ -4333,13 +4862,13 @@
         </is>
       </c>
       <c r="C80" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D80" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>50013</v>
+        <v>120705</v>
       </c>
     </row>
     <row r="81">
@@ -4354,13 +4883,13 @@
         </is>
       </c>
       <c r="C81" s="14" t="n">
-        <v>1291</v>
+        <v>15513</v>
       </c>
       <c r="D81" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>51303</v>
+        <v>136218</v>
       </c>
     </row>
     <row r="82">
@@ -4375,13 +4904,13 @@
         </is>
       </c>
       <c r="C82" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D82" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>52594</v>
+        <v>137783</v>
       </c>
     </row>
     <row r="83">
@@ -4396,13 +4925,13 @@
         </is>
       </c>
       <c r="C83" s="14" t="n">
-        <v>6865</v>
+        <v>8538</v>
       </c>
       <c r="D83" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>59459</v>
+        <v>146321</v>
       </c>
     </row>
     <row r="84">
@@ -4417,13 +4946,13 @@
         </is>
       </c>
       <c r="C84" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>-38250</v>
+        <v>-36611</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>28074</v>
+        <v>118249</v>
       </c>
     </row>
     <row r="85">
@@ -4438,13 +4967,13 @@
         </is>
       </c>
       <c r="C85" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D85" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>34939</v>
+        <v>118249</v>
       </c>
     </row>
     <row r="86">
@@ -4459,13 +4988,13 @@
         </is>
       </c>
       <c r="C86" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D86" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>40513</v>
+        <v>118249</v>
       </c>
     </row>
     <row r="87">
@@ -4480,13 +5009,13 @@
         </is>
       </c>
       <c r="C87" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D87" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>46088</v>
+        <v>118249</v>
       </c>
     </row>
     <row r="88">
@@ -4501,13 +5030,13 @@
         </is>
       </c>
       <c r="C88" s="14" t="n">
-        <v>1291</v>
+        <v>0</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>42378</v>
+        <v>118249</v>
       </c>
     </row>
     <row r="89">
@@ -4522,13 +5051,13 @@
         </is>
       </c>
       <c r="C89" s="14" t="n">
-        <v>1291</v>
+        <v>25616</v>
       </c>
       <c r="D89" s="14" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>43669</v>
+        <v>138865</v>
       </c>
     </row>
     <row r="90">
@@ -4543,13 +5072,13 @@
         </is>
       </c>
       <c r="C90" s="14" t="n">
-        <v>6865</v>
+        <v>8539</v>
       </c>
       <c r="D90" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>50534</v>
+        <v>147404</v>
       </c>
     </row>
     <row r="91">
@@ -4564,13 +5093,13 @@
         </is>
       </c>
       <c r="C91" s="14" t="n">
-        <v>47365</v>
+        <v>58423</v>
       </c>
       <c r="D91" s="14" t="n">
-        <v>-56160</v>
+        <v>-61668</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>41739</v>
+        <v>144159</v>
       </c>
     </row>
     <row r="92">
@@ -4585,13 +5114,13 @@
         </is>
       </c>
       <c r="C92" s="14" t="n">
-        <v>6865</v>
+        <v>0</v>
       </c>
       <c r="D92" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>48604</v>
+        <v>144159</v>
       </c>
     </row>
     <row r="93">
@@ -4606,13 +5135,13 @@
         </is>
       </c>
       <c r="C93" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D93" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>54178</v>
+        <v>144159</v>
       </c>
     </row>
     <row r="94">
@@ -4627,13 +5156,13 @@
         </is>
       </c>
       <c r="C94" s="14" t="n">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="D94" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>59752</v>
+        <v>144159</v>
       </c>
     </row>
     <row r="95">
@@ -4648,13 +5177,13 @@
         </is>
       </c>
       <c r="C95" s="14" t="n">
-        <v>1291</v>
+        <v>20922</v>
       </c>
       <c r="D95" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>61043</v>
+        <v>165081</v>
       </c>
     </row>
     <row r="96">
@@ -4669,13 +5198,13 @@
         </is>
       </c>
       <c r="C96" s="14" t="n">
-        <v>1291</v>
+        <v>1565</v>
       </c>
       <c r="D96" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>62334</v>
+        <v>166646</v>
       </c>
     </row>
   </sheetData>
@@ -4684,7 +5213,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-10/cash-payroll.xlsx
+++ b/media/exports/reports/2026-10/cash-payroll.xlsx
@@ -868,7 +868,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Call-out 15, September</t>
+          <t>Call-out CO-49240</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -2049,7 +2049,7 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Call-out 9, September</t>
+          <t>Call-out CO-49233</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -2076,7 +2076,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Call-out 32, September</t>
+          <t>Call-out CO-49260</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Call-out 28, September</t>
+          <t>Call-out CO-49255</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -2130,7 +2130,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Call-out 49, September</t>
+          <t>Call-out CO-49280</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -2157,7 +2157,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Call-out 63, September</t>
+          <t>Call-out CO-49296</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -2184,7 +2184,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Call-out 50, September</t>
+          <t>Call-out CO-49281</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -2211,7 +2211,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Call-out 22, September</t>
+          <t>Call-out CO-49248</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -2238,7 +2238,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Call-out 38, September</t>
+          <t>Call-out CO-49267</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Call-out 26, September</t>
+          <t>Call-out CO-49253</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -2292,7 +2292,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Call-out 31, September</t>
+          <t>Call-out CO-49259</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -2319,7 +2319,7 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Call-out 43, September</t>
+          <t>Call-out CO-49273</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -2402,7 +2402,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2448,7 +2448,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3264,7 +3264,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5213,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-10/cash-payroll.xlsx
+++ b/media/exports/reports/2026-10/cash-payroll.xlsx
@@ -12,11 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Cash_at_bank_6_Oct">'Report'!$B$8</definedName>
-    <definedName name="Paid_to_employees_in_November">'Report'!$B$9</definedName>
-    <definedName name="After_the_tightest_pay_run_26_Nov">'Report'!$B$10</definedName>
-    <definedName name="Lowest_point_next_13_weeks">'Report'!$B$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$J$76</definedName>
+    <definedName name="Cash_at_bank_6_Oct">'Report'!$B$9</definedName>
+    <definedName name="Paid_to_employees_in_November">'Report'!$B$10</definedName>
+    <definedName name="After_the_tightest_pay_run_26_Nov">'Report'!$B$11</definedName>
+    <definedName name="Lowest_point_next_13_weeks">'Report'!$B$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$J$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$108</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$96</definedName>
@@ -54,6 +54,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -74,11 +79,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -116,25 +116,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -142,12 +145,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -333,12 +336,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$15:$A$20</f>
+              <f>'Report'!$A$16:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$15:$B$20</f>
+              <f>'Report'!$B$16:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -485,7 +488,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2340000"/>
@@ -836,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -868,7 +871,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -876,175 +879,179 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Yes: $98,068 forecast in the bank after the 26 November pay run, the tightest in November, and at least one pay run in reserve for all 13 weeks. It depends on $86,470 of overdue invoices arriving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>A 13-week cash forecast from 2pm on 6 October: cash at bank, plus what customers owe on their usual payment dates and new work at its recent rate, less pay runs, supplier bills, the BAS and finance on their due dates. Every day opens its workings.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Cash at bank, 6 Oct</t>
         </is>
       </c>
-      <c r="B8" s="6">
+      <c r="B9" s="7">
         <f>Workings!B11</f>
         <v/>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>2pm, still moving</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Paid to employees in November</t>
         </is>
       </c>
-      <c r="B9" s="6">
+      <c r="B10" s="7">
         <f>Workings!B20</f>
         <v/>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>2 fortnightly pay runs, net pay + super</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>After the tightest pay run, 26 Nov</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B11" s="7">
         <f>Workings!B34</f>
         <v/>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>buffer: one pay run, $36,611</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Lowest point, next 13 weeks</t>
         </is>
       </c>
-      <c r="B11" s="6">
+      <c r="B12" s="7">
         <f>Workings!B48</f>
         <v/>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>30 November</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>November: where the cash comes from and goes (forecast)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>November: where the cash comes from and goes (forecast)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Unpaid invoices collected</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B16" s="7">
         <f>Workings!B55</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>New work collected</t>
         </is>
       </c>
-      <c r="B16" s="6">
+      <c r="B17" s="7">
         <f>Workings!B62</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pay runs (2)</t>
-        </is>
-      </c>
-      <c r="B17" s="6">
-        <f>Workings!B71</f>
-        <v/>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Pay runs (2)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>-73222</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Suppliers and overheads</t>
         </is>
       </c>
-      <c r="B18" s="6">
+      <c r="B19" s="7">
         <f>Workings!B84</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>BAS (GST and PAYG)</t>
         </is>
       </c>
-      <c r="B19" s="6">
+      <c r="B20" s="7">
         <f>Workings!B90</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Interest and equipment finance</t>
         </is>
       </c>
-      <c r="B20" s="6">
-        <f>Workings!B97</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="B21" s="7" t="n">
+        <v>-7160</v>
+      </c>
+    </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
@@ -1052,1365 +1059,1367 @@
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Cash at bank, every day: actual to 6 Oct, then forecast to 5 Jan: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>13 weeks, week by week</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Week ending</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Cash at start</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Unpaid invoices collected</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>New work collected</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Pay runs</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>Suppliers and overheads</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>BAS (GST and PAYG)</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>Interest and finance</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>Cash at end</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>Lowest in the week</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>13 Oct</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>$115,211</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>$111,493</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>$226,704</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>$115,211</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>20 Oct</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>$226,704</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>$15,840</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>$7,823</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>$153,168</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>$132,634</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>$153,168</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>$12,100</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>$7,824</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>$173,092</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>$154,733</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>3 Nov</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>$173,092</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>$109,285</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>$7,823</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>($86,253)</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>($6,080)</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>$100,668</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>$67,057</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>10 Nov</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>$100,668</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>$28,746</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>$129,414</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>$102,233</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>17 Nov</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>$129,414</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>$42,693</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
+      <c r="I39" s="12" t="inlineStr">
         <is>
           <t>$74,908</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>$73,344</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>24 Nov</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>$74,908</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>$42,694</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I40" s="12" t="inlineStr">
         <is>
           <t>$117,602</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>$83,447</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>1 Dec</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>$117,602</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>$92,578</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>($6,080)</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
         <is>
           <t>$106,901</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>$55,452</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>8 Dec</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>$106,901</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>$42,694</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>$149,595</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>$115,440</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>15 Dec</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>$149,595</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>$42,693</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>$95,089</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>$95,089</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>22 Dec</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>$95,089</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>$42,694</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>$137,783</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>$103,628</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>29 Dec</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>$137,783</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>$42,693</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>($36,611)</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>($5,000)</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>$138,865</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>$118,249</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>5 Jan</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>$138,865</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>$89,449</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>($60,588)</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>($1,080)</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>$166,646</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>$144,159</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Invoices past the customer's usual payment date ($86,470): the forecast assumes these arrive within a week</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Customer or job</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Invoiced</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Amount (incl. GST)</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Usually pays in (days)</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>Days since invoiced</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Wacol warehouse switchboard</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>4 Sep</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>$57,640</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Milton office tower</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>$5,170</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Rocklea factory</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>$4,785</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Bulimba school</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>$3,465</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>West End brewery</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>$3,190</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>$2,970</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>Newstead gym</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>1 Sep</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>$1,980</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49240</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>15 Sep</t>
         </is>
       </c>
-      <c r="C56" s="11" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>$932</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49233</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>22 Sep</t>
         </is>
       </c>
-      <c r="C57" s="11" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>$917</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E57" s="11" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49260</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>21 Sep</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>$706</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49255</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>25 Sep</t>
         </is>
       </c>
-      <c r="C59" s="11" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>$659</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49280</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>27 Sep</t>
         </is>
       </c>
-      <c r="C60" s="11" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
         <is>
           <t>$645</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49296</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>15 Sep</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr">
+      <c r="C62" s="12" t="inlineStr">
         <is>
           <t>$635</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49281</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>28 Sep</t>
         </is>
       </c>
-      <c r="C62" s="11" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
         <is>
           <t>$598</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49248</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>17 Sep</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C64" s="12" t="inlineStr">
         <is>
           <t>$535</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49267</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>23 Sep</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>$459</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49253</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>26 Sep</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C66" s="12" t="inlineStr">
         <is>
           <t>$441</t>
         </is>
       </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49259</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>13 Sep</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C67" s="12" t="inlineStr">
         <is>
           <t>$416</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>Call-out CO-49273</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>16 Sep</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr">
         <is>
           <t>$327</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E67" s="11" t="inlineStr">
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t>How the 30 September forecast has done so far</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="45" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>For 5 October it said $133,401; the bank says $104,453, $28,948 less. $31,304 of it is 11 invoices expected by then and not yet paid, the largest Milton office tower ($5,170). (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="12" t="inlineStr">
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Cash at bank was $115,211 at 2pm on 6 October. November has 2 pay runs ($73,222). The tightest is 26 November: $98,068 left after paying wages, $61,457 more than a pay run in reserve. The lowest point in the 13 weeks is $55,452 on 30 November.</t>
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="12" t="inlineStr">
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>19 invoices ($86,470) are already past the customer's usual payment date; the forecast assumes they arrive within a week. Without them, the lowest point would be ($31,018). The July to September BAS ($86,253) is due 28 October: GST $32,817, PAYG withheld $47,754 and the PAYG instalment $5,682.</t>
         </is>
       </c>
     </row>
-    <row r="77"/>
     <row r="78"/>
+    <row r="79"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A71:D71"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="30" min="0" max="16383" man="1"/>
-    <brk id="71" min="0" max="16383" man="1"/>
+    <brk id="31" min="0" max="16383" man="1"/>
+    <brk id="72" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2448,28 +2457,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Cash at bank, 2pm on 6 October</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Opening balance + every day's money in − money out</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>6 Oct</t>
         </is>
@@ -2481,7 +2490,7 @@
           <t>Cash at bank, 31 July (opening balance)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="15" t="n">
         <v>88000</v>
       </c>
     </row>
@@ -2491,7 +2500,7 @@
           <t>Money in, 1 August to 6 October</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="15" t="n">
         <v>445130</v>
       </c>
     </row>
@@ -2501,17 +2510,17 @@
           <t>Money out, 1 August to 6 October</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="15" t="n">
         <v>-417919</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Cash at bank</t>
         </is>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="17">
         <f>B8+B9+B10</f>
         <v/>
       </c>
@@ -2526,22 +2535,22 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Pay runs in November</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Number of fortnightly pay runs × the cash each one takes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>November</t>
         </is>
@@ -2553,7 +2562,7 @@
           <t>Last pay run, net pay + super (1 October)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="15" t="n">
         <v>36611</v>
       </c>
     </row>
@@ -2563,17 +2572,17 @@
           <t>Pay runs in November (12 Nov, 26 Nov)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Paid to employees and their super funds in November</t>
         </is>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="17">
         <f>B18*B19</f>
         <v/>
       </c>
@@ -2588,22 +2597,22 @@
     <row r="22"/>
     <row r="23"/>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Forecast cash at bank, 26 Nov 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Yesterday's cash + money in − money out</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>26 Nov</t>
         </is>
@@ -2615,7 +2624,7 @@
           <t>Cash at bank, end of the day before</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="15" t="n">
         <v>126140</v>
       </c>
     </row>
@@ -2625,7 +2634,7 @@
           <t>Unpaid invoices expected (incl. GST)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2635,7 +2644,7 @@
           <t>New work expected to be paid (incl. GST)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="15" t="n">
         <v>8539</v>
       </c>
     </row>
@@ -2645,7 +2654,7 @@
           <t>Pay run (net pay + super)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="15" t="n">
         <v>-36611</v>
       </c>
     </row>
@@ -2655,7 +2664,7 @@
           <t>Suppliers and overheads (incl. GST)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2665,7 +2674,7 @@
           <t>BAS: GST, PAYG withheld and PAYG instalment</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2675,17 +2684,17 @@
           <t>Interest and equipment finance</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Cash at bank, end of the day</t>
         </is>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <f>B27+B28+B29+B30+B31+B32+B33</f>
         <v/>
       </c>
@@ -2700,22 +2709,22 @@
     <row r="36"/>
     <row r="37"/>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Forecast cash at bank, 30 Nov 2026</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Yesterday's cash + money in − money out</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr"/>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>30 Nov</t>
         </is>
@@ -2727,7 +2736,7 @@
           <t>Cash at bank, end of the day before</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n">
+      <c r="B41" s="15" t="n">
         <v>106607</v>
       </c>
     </row>
@@ -2737,7 +2746,7 @@
           <t>Unpaid invoices expected (incl. GST)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
+      <c r="B42" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2747,7 +2756,7 @@
           <t>New work expected to be paid (incl. GST)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="15" t="n">
         <v>15513</v>
       </c>
     </row>
@@ -2757,7 +2766,7 @@
           <t>Pay run (net pay + super)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2767,7 +2776,7 @@
           <t>Suppliers and overheads (incl. GST)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
+      <c r="B45" s="15" t="n">
         <v>-60588</v>
       </c>
     </row>
@@ -2777,7 +2786,7 @@
           <t>BAS: GST, PAYG withheld and PAYG instalment</t>
         </is>
       </c>
-      <c r="B46" s="14" t="n">
+      <c r="B46" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2787,17 +2796,17 @@
           <t>Interest and equipment finance</t>
         </is>
       </c>
-      <c r="B47" s="14" t="n">
+      <c r="B47" s="15" t="n">
         <v>-6080</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Cash at bank, end of the day</t>
         </is>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="17">
         <f>B41+B42+B43+B44+B45+B46+B47</f>
         <v/>
       </c>
@@ -2812,34 +2821,34 @@
     <row r="50"/>
     <row r="51"/>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Unpaid invoices collected in November</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Each invoice unpaid at the start, on its customer's usual payment date (next banking day)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr"/>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr"/>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Expected in the month (incl. GST)</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>90585</v>
       </c>
     </row>
@@ -2853,34 +2862,34 @@
     <row r="57"/>
     <row r="58"/>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>New work collected in November</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Contract fees (1st of the month, on each contract's terms) + installations and call-outs at the last three months' run rate</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr"/>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr"/>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="inlineStr">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>Expected in the month (incl. GST)</t>
         </is>
       </c>
-      <c r="B62" s="16" t="n">
+      <c r="B62" s="17" t="n">
         <v>158391</v>
       </c>
     </row>
@@ -2894,22 +2903,22 @@
     <row r="64"/>
     <row r="65"/>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>Pay runs in November</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>Number of fortnightly pay runs × the cash each one takes</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr"/>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr"/>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>November</t>
         </is>
@@ -2921,7 +2930,7 @@
           <t>Last pay run, net pay + super (1 October)</t>
         </is>
       </c>
-      <c r="B69" s="14" t="n">
+      <c r="B69" s="15" t="n">
         <v>36611</v>
       </c>
     </row>
@@ -2931,17 +2940,17 @@
           <t>Pay runs in November (12 Nov, 26 Nov)</t>
         </is>
       </c>
-      <c r="B70" s="14" t="n">
+      <c r="B70" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="15" t="inlineStr">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t>Paid to employees and their super funds in November</t>
         </is>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="17">
         <f>B69*B70</f>
         <v/>
       </c>
@@ -2956,22 +2965,22 @@
     <row r="73"/>
     <row r="74"/>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" s="14" t="inlineStr">
         <is>
           <t>Suppliers and overheads in November</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>Last month's bills (trade creditors) + the month's overheads, half on the 15th and half at month end, on banking days</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr"/>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr"/>
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>November</t>
         </is>
@@ -2983,7 +2992,7 @@
           <t>October's bills for materials and subcontractors, incl. GST (estimate: the latest month's)</t>
         </is>
       </c>
-      <c r="B78" s="14" t="n">
+      <c r="B78" s="15" t="n">
         <v>85866</v>
       </c>
     </row>
@@ -2993,7 +3002,7 @@
           <t>Overheads, incl. GST (at September's level)</t>
         </is>
       </c>
-      <c r="B79" s="14" t="n">
+      <c r="B79" s="15" t="n">
         <v>35310</v>
       </c>
     </row>
@@ -3003,7 +3012,7 @@
           <t>November's supplier bills</t>
         </is>
       </c>
-      <c r="B80" s="14">
+      <c r="B80" s="15">
         <f>B78+B79</f>
         <v/>
       </c>
@@ -3014,7 +3023,7 @@
           <t>October run due 31 October, lands Mon 2 Nov (31 Oct isn't a banking day): paid in November</t>
         </is>
       </c>
-      <c r="B81" s="14" t="n">
+      <c r="B81" s="15" t="n">
         <v>-60588</v>
       </c>
     </row>
@@ -3024,7 +3033,7 @@
           <t>November run due 15 November, lands Mon 16 Nov (15 Nov isn't a banking day): paid in November</t>
         </is>
       </c>
-      <c r="B82" s="14" t="n">
+      <c r="B82" s="15" t="n">
         <v>-60588</v>
       </c>
     </row>
@@ -3034,17 +3043,17 @@
           <t>November run due 30 November: paid in November</t>
         </is>
       </c>
-      <c r="B83" s="14" t="n">
+      <c r="B83" s="15" t="n">
         <v>-60588</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="15" t="inlineStr">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Paid in November</t>
         </is>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="17">
         <f>B81+B82+B83</f>
         <v/>
       </c>
@@ -3052,34 +3061,34 @@
     <row r="85"/>
     <row r="86"/>
     <row r="87">
-      <c r="A87" s="13" t="inlineStr">
+      <c r="A87" s="14" t="inlineStr">
         <is>
           <t>BAS in November</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>GST on sales − GST credits + PAYG withheld + PAYG instalment, for the quarter, due on the 28th (quarterly, self-lodged)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr"/>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="15" t="inlineStr">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t>BAS paid in November</t>
         </is>
       </c>
-      <c r="B90" s="16" t="n">
+      <c r="B90" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3093,56 +3102,56 @@
     <row r="92"/>
     <row r="93"/>
     <row r="94">
-      <c r="A94" s="13" t="inlineStr">
+      <c r="A94" s="14" t="inlineStr">
         <is>
           <t>Interest and equipment finance in November</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>Interest at month end + the equipment finance repayment on the 28th (no GST on either)</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr"/>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="A96" s="5" t="inlineStr"/>
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="15" t="inlineStr">
+      <c r="A97" s="16" t="inlineStr">
         <is>
           <t>Paid in the month</t>
         </is>
       </c>
-      <c r="B97" s="16" t="n">
+      <c r="B97" s="17" t="n">
         <v>7160</v>
       </c>
     </row>
     <row r="98"/>
     <row r="99"/>
     <row r="100">
-      <c r="A100" s="13" t="inlineStr">
+      <c r="A100" s="14" t="inlineStr">
         <is>
           <t>Forecast made 30 September against the bank, 5 October</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>Actual cash − forecast cash</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr"/>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr"/>
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>5 Oct</t>
         </is>
@@ -3154,7 +3163,7 @@
           <t>Forecast for 5 October</t>
         </is>
       </c>
-      <c r="B103" s="14" t="n">
+      <c r="B103" s="15" t="n">
         <v>133401</v>
       </c>
     </row>
@@ -3164,7 +3173,7 @@
           <t>Actual, 5 October</t>
         </is>
       </c>
-      <c r="B104" s="14" t="n">
+      <c r="B104" s="15" t="n">
         <v>104453</v>
       </c>
     </row>
@@ -3174,7 +3183,7 @@
           <t>Actual − forecast</t>
         </is>
       </c>
-      <c r="B105" s="14">
+      <c r="B105" s="15">
         <f>B104-B103</f>
         <v/>
       </c>
@@ -3185,17 +3194,17 @@
           <t>Of which: invoices expected by then, not yet paid</t>
         </is>
       </c>
-      <c r="B106" s="14" t="n">
+      <c r="B106" s="15" t="n">
         <v>-31304</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="15" t="inlineStr">
+      <c r="A107" s="16" t="inlineStr">
         <is>
           <t>Everything else (timing of other money in and out)</t>
         </is>
       </c>
-      <c r="B107" s="16">
+      <c r="B107" s="17">
         <f>B105-B106</f>
         <v/>
       </c>
@@ -3216,7 +3225,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3264,1946 +3273,1946 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Actual or forecast</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Money in</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Money out</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Cash at bank</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="n">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="n">
         <v>115211</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
         <v>832</v>
       </c>
-      <c r="D7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14" t="n">
+      <c r="D7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15" t="n">
         <v>116043</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
         <v>23599</v>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14" t="n">
+      <c r="D8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>139642</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="14" t="n">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15" t="n">
         <v>139642</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="14" t="n">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15" t="n">
         <v>139642</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
         <v>592</v>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="14" t="n">
+      <c r="D11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15" t="n">
         <v>140234</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
         <v>86470</v>
       </c>
-      <c r="D12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="14" t="n">
+      <c r="D12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
         <v>226704</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="14" t="n">
+      <c r="D13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15" t="n">
         <v>228269</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
         <v>1564</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>-97199</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <v>132634</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="14" t="n">
+      <c r="D15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15" t="n">
         <v>134199</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="14" t="n">
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15" t="n">
         <v>134199</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="14" t="n">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15" t="n">
         <v>134199</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
         <v>17405</v>
       </c>
-      <c r="D18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="14" t="n">
+      <c r="D18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15" t="n">
         <v>151604</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
         <v>1564</v>
       </c>
-      <c r="D19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="14" t="n">
+      <c r="D19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="15" t="n">
         <v>153168</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="14" t="n">
+      <c r="D20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15" t="n">
         <v>154733</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="14" t="n">
+      <c r="D21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="n">
         <v>156298</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
         <v>13665</v>
       </c>
-      <c r="D22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="14" t="n">
+      <c r="D22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="n">
         <v>169963</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="14" t="n">
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="15" t="n">
         <v>169963</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="14" t="n">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="15" t="n">
         <v>169963</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
         <v>1564</v>
       </c>
-      <c r="D25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="14" t="n">
+      <c r="D25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="15" t="n">
         <v>171527</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="14" t="n">
+      <c r="D26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="15" t="n">
         <v>173092</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="15" t="n">
         <v>-91253</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="15" t="n">
         <v>83404</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
         <v>20264</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="15" t="n">
         <v>67057</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="14" t="n">
+      <c r="D29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="15" t="n">
         <v>68622</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="14" t="n">
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="15" t="n">
         <v>68622</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>2026-11-01</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="14" t="n">
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="15" t="n">
         <v>68622</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
         <v>92150</v>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D32" s="15" t="n">
         <v>-61668</v>
       </c>
-      <c r="E32" s="14" t="n">
+      <c r="E32" s="15" t="n">
         <v>99104</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
         <v>1564</v>
       </c>
-      <c r="D33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="14" t="n">
+      <c r="D33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="15" t="n">
         <v>100668</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>2026-11-04</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D34" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="14" t="n">
+      <c r="D34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="15" t="n">
         <v>102233</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="14" t="n">
+      <c r="D35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="15" t="n">
         <v>103798</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
         <v>8538</v>
       </c>
-      <c r="D36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="14" t="n">
+      <c r="D36" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="15" t="n">
         <v>112336</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>2026-11-07</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="14" t="n">
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="15" t="n">
         <v>112336</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>2026-11-08</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="14" t="n">
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="15" t="n">
         <v>112336</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n">
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
         <v>15513</v>
       </c>
-      <c r="D39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="14" t="n">
+      <c r="D39" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="15" t="n">
         <v>127849</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D40" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="14" t="n">
+      <c r="D40" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="15" t="n">
         <v>129414</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>2026-11-11</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="14" t="n">
+      <c r="D41" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="15" t="n">
         <v>137953</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="n">
         <v>8538</v>
       </c>
-      <c r="D42" s="14" t="n">
+      <c r="D42" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E42" s="14" t="n">
+      <c r="E42" s="15" t="n">
         <v>109880</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>2026-11-13</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D43" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="14" t="n">
+      <c r="D43" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="15" t="n">
         <v>118419</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>2026-11-14</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="14" t="n">
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="15" t="n">
         <v>118419</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>2026-11-15</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="14" t="n">
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="15" t="n">
         <v>118419</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>2026-11-16</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="n">
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="n">
         <v>15513</v>
       </c>
-      <c r="D46" s="14" t="n">
+      <c r="D46" s="15" t="n">
         <v>-60588</v>
       </c>
-      <c r="E46" s="14" t="n">
+      <c r="E46" s="15" t="n">
         <v>73344</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>2026-11-17</t>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="n">
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="n">
         <v>1564</v>
       </c>
-      <c r="D47" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="14" t="n">
+      <c r="D47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="15" t="n">
         <v>74908</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>2026-11-18</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="n">
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D48" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="14" t="n">
+      <c r="D48" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="15" t="n">
         <v>83447</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>2026-11-19</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n">
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D49" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="14" t="n">
+      <c r="D49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="15" t="n">
         <v>91986</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n">
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n">
         <v>8538</v>
       </c>
-      <c r="D50" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="14" t="n">
+      <c r="D50" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="15" t="n">
         <v>100524</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>2026-11-21</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="14" t="n">
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="15" t="n">
         <v>100524</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>2026-11-22</t>
         </is>
       </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="14" t="n">
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="15" t="n">
         <v>100524</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="n">
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="n">
         <v>15513</v>
       </c>
-      <c r="D53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="14" t="n">
+      <c r="D53" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="15" t="n">
         <v>116037</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>2026-11-24</t>
         </is>
       </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n">
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D54" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="14" t="n">
+      <c r="D54" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="15" t="n">
         <v>117602</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="n">
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n">
         <v>8538</v>
       </c>
-      <c r="D55" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="14" t="n">
+      <c r="D55" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="15" t="n">
         <v>126140</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>2026-11-26</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="n">
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D56" s="14" t="n">
+      <c r="D56" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E56" s="14" t="n">
+      <c r="E56" s="15" t="n">
         <v>98068</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>2026-11-27</t>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="n">
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D57" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="14" t="n">
+      <c r="D57" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="15" t="n">
         <v>106607</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="A58" s="18" t="inlineStr">
         <is>
           <t>2026-11-28</t>
         </is>
       </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="14" t="n">
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="15" t="n">
         <v>106607</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>2026-11-29</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="14" t="n">
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="15" t="n">
         <v>106607</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="17" t="inlineStr">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="n">
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="n">
         <v>15513</v>
       </c>
-      <c r="D60" s="14" t="n">
+      <c r="D60" s="15" t="n">
         <v>-66668</v>
       </c>
-      <c r="E60" s="14" t="n">
+      <c r="E60" s="15" t="n">
         <v>55452</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="17" t="inlineStr">
+      <c r="A61" s="18" t="inlineStr">
         <is>
           <t>2026-12-01</t>
         </is>
       </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="n">
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="n">
         <v>51449</v>
       </c>
-      <c r="D61" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="14" t="n">
+      <c r="D61" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="15" t="n">
         <v>106901</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="17" t="inlineStr">
+      <c r="A62" s="18" t="inlineStr">
         <is>
           <t>2026-12-02</t>
         </is>
       </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D62" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="14" t="n">
+      <c r="D62" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="15" t="n">
         <v>115440</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="inlineStr">
+      <c r="A63" s="18" t="inlineStr">
         <is>
           <t>2026-12-03</t>
         </is>
       </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n">
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D63" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="14" t="n">
+      <c r="D63" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="15" t="n">
         <v>123979</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="A64" s="18" t="inlineStr">
         <is>
           <t>2026-12-04</t>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="n">
         <v>8538</v>
       </c>
-      <c r="D64" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="14" t="n">
+      <c r="D64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="15" t="n">
         <v>132517</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="17" t="inlineStr">
+      <c r="A65" s="18" t="inlineStr">
         <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="14" t="n">
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="15" t="n">
         <v>132517</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="17" t="inlineStr">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t>2026-12-06</t>
         </is>
       </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="14" t="n">
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="15" t="n">
         <v>132517</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="17" t="inlineStr">
+      <c r="A67" s="18" t="inlineStr">
         <is>
           <t>2026-12-07</t>
         </is>
       </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="n">
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="n">
         <v>15513</v>
       </c>
-      <c r="D67" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="14" t="n">
+      <c r="D67" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="15" t="n">
         <v>148030</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="17" t="inlineStr">
+      <c r="A68" s="18" t="inlineStr">
         <is>
           <t>2026-12-08</t>
         </is>
       </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="n">
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D68" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="14" t="n">
+      <c r="D68" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="15" t="n">
         <v>149595</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="17" t="inlineStr">
+      <c r="A69" s="18" t="inlineStr">
         <is>
           <t>2026-12-09</t>
         </is>
       </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="n">
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="n">
         <v>8538</v>
       </c>
-      <c r="D69" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="14" t="n">
+      <c r="D69" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="15" t="n">
         <v>158133</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="17" t="inlineStr">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t>2026-12-10</t>
         </is>
       </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="n">
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D70" s="14" t="n">
+      <c r="D70" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E70" s="14" t="n">
+      <c r="E70" s="15" t="n">
         <v>130061</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="17" t="inlineStr">
+      <c r="A71" s="18" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
       </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C71" s="14" t="n">
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D71" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="14" t="n">
+      <c r="D71" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="15" t="n">
         <v>138600</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="17" t="inlineStr">
+      <c r="A72" s="18" t="inlineStr">
         <is>
           <t>2026-12-12</t>
         </is>
       </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="14" t="n">
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="15" t="n">
         <v>138600</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="17" t="inlineStr">
+      <c r="A73" s="18" t="inlineStr">
         <is>
           <t>2026-12-13</t>
         </is>
       </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="14" t="n">
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="15" t="n">
         <v>138600</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="17" t="inlineStr">
+      <c r="A74" s="18" t="inlineStr">
         <is>
           <t>2026-12-14</t>
         </is>
       </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C74" s="14" t="n">
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="n">
         <v>15512</v>
       </c>
-      <c r="D74" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="14" t="n">
+      <c r="D74" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="15" t="n">
         <v>154112</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="17" t="inlineStr">
+      <c r="A75" s="18" t="inlineStr">
         <is>
           <t>2026-12-15</t>
         </is>
       </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="n">
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D75" s="14" t="n">
+      <c r="D75" s="15" t="n">
         <v>-60588</v>
       </c>
-      <c r="E75" s="14" t="n">
+      <c r="E75" s="15" t="n">
         <v>95089</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="17" t="inlineStr">
+      <c r="A76" s="18" t="inlineStr">
         <is>
           <t>2026-12-16</t>
         </is>
       </c>
-      <c r="B76" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C76" s="14" t="n">
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D76" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="14" t="n">
+      <c r="D76" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="15" t="n">
         <v>103628</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="17" t="inlineStr">
+      <c r="A77" s="18" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="n">
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D77" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="14" t="n">
+      <c r="D77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="15" t="n">
         <v>112167</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="17" t="inlineStr">
+      <c r="A78" s="18" t="inlineStr">
         <is>
           <t>2026-12-18</t>
         </is>
       </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C78" s="14" t="n">
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="n">
         <v>8538</v>
       </c>
-      <c r="D78" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="14" t="n">
+      <c r="D78" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="15" t="n">
         <v>120705</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="17" t="inlineStr">
+      <c r="A79" s="18" t="inlineStr">
         <is>
           <t>2026-12-19</t>
         </is>
       </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="14" t="n">
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="15" t="n">
         <v>120705</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="17" t="inlineStr">
+      <c r="A80" s="18" t="inlineStr">
         <is>
           <t>2026-12-20</t>
         </is>
       </c>
-      <c r="B80" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C80" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="14" t="n">
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="15" t="n">
         <v>120705</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="17" t="inlineStr">
+      <c r="A81" s="18" t="inlineStr">
         <is>
           <t>2026-12-21</t>
         </is>
       </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="n">
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="n">
         <v>15513</v>
       </c>
-      <c r="D81" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="14" t="n">
+      <c r="D81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="15" t="n">
         <v>136218</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="17" t="inlineStr">
+      <c r="A82" s="18" t="inlineStr">
         <is>
           <t>2026-12-22</t>
         </is>
       </c>
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C82" s="14" t="n">
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D82" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="14" t="n">
+      <c r="D82" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="15" t="n">
         <v>137783</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="17" t="inlineStr">
+      <c r="A83" s="18" t="inlineStr">
         <is>
           <t>2026-12-23</t>
         </is>
       </c>
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="n">
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="n">
         <v>8538</v>
       </c>
-      <c r="D83" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="14" t="n">
+      <c r="D83" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="15" t="n">
         <v>146321</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="17" t="inlineStr">
+      <c r="A84" s="18" t="inlineStr">
         <is>
           <t>2026-12-24</t>
         </is>
       </c>
-      <c r="B84" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C84" s="14" t="n">
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D84" s="14" t="n">
+      <c r="D84" s="15" t="n">
         <v>-36611</v>
       </c>
-      <c r="E84" s="14" t="n">
+      <c r="E84" s="15" t="n">
         <v>118249</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="17" t="inlineStr">
+      <c r="A85" s="18" t="inlineStr">
         <is>
           <t>2026-12-25</t>
         </is>
       </c>
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="14" t="n">
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="15" t="n">
         <v>118249</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="17" t="inlineStr">
+      <c r="A86" s="18" t="inlineStr">
         <is>
           <t>2026-12-26</t>
         </is>
       </c>
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C86" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="14" t="n">
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="15" t="n">
         <v>118249</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="17" t="inlineStr">
+      <c r="A87" s="18" t="inlineStr">
         <is>
           <t>2026-12-27</t>
         </is>
       </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C87" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="14" t="n">
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="15" t="n">
         <v>118249</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="17" t="inlineStr">
+      <c r="A88" s="18" t="inlineStr">
         <is>
           <t>2026-12-28</t>
         </is>
       </c>
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="14" t="n">
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="15" t="n">
         <v>118249</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="17" t="inlineStr">
+      <c r="A89" s="18" t="inlineStr">
         <is>
           <t>2026-12-29</t>
         </is>
       </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="n">
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="n">
         <v>25616</v>
       </c>
-      <c r="D89" s="14" t="n">
+      <c r="D89" s="15" t="n">
         <v>-5000</v>
       </c>
-      <c r="E89" s="14" t="n">
+      <c r="E89" s="15" t="n">
         <v>138865</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="17" t="inlineStr">
+      <c r="A90" s="18" t="inlineStr">
         <is>
           <t>2026-12-30</t>
         </is>
       </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="n">
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="n">
         <v>8539</v>
       </c>
-      <c r="D90" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="14" t="n">
+      <c r="D90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="15" t="n">
         <v>147404</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="17" t="inlineStr">
+      <c r="A91" s="18" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="n">
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="n">
         <v>58423</v>
       </c>
-      <c r="D91" s="14" t="n">
+      <c r="D91" s="15" t="n">
         <v>-61668</v>
       </c>
-      <c r="E91" s="14" t="n">
+      <c r="E91" s="15" t="n">
         <v>144159</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="17" t="inlineStr">
+      <c r="A92" s="18" t="inlineStr">
         <is>
           <t>2027-01-01</t>
         </is>
       </c>
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="14" t="n">
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="15" t="n">
         <v>144159</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="17" t="inlineStr">
+      <c r="A93" s="18" t="inlineStr">
         <is>
           <t>2027-01-02</t>
         </is>
       </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="14" t="n">
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="15" t="n">
         <v>144159</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="17" t="inlineStr">
+      <c r="A94" s="18" t="inlineStr">
         <is>
           <t>2027-01-03</t>
         </is>
       </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C94" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="14" t="n">
+      <c r="B94" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="15" t="n">
         <v>144159</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="17" t="inlineStr">
+      <c r="A95" s="18" t="inlineStr">
         <is>
           <t>2027-01-04</t>
         </is>
       </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C95" s="14" t="n">
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="n">
         <v>20922</v>
       </c>
-      <c r="D95" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="14" t="n">
+      <c r="D95" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="15" t="n">
         <v>165081</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="17" t="inlineStr">
+      <c r="A96" s="18" t="inlineStr">
         <is>
           <t>2027-01-05</t>
         </is>
       </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="C96" s="14" t="n">
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="n">
         <v>1565</v>
       </c>
-      <c r="D96" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="14" t="n">
+      <c r="D96" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="15" t="n">
         <v>166646</v>
       </c>
     </row>
@@ -5213,7 +5222,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 cash-payroll.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
